--- a/AVUwinnersCM/winners_report.xlsx
+++ b/AVUwinnersCM/winners_report.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 All-Time'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last 21 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Last Month (March 2026)'!$A$3:$N$53</definedName>
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2139,7 +2139,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2757,71 +2757,71 @@
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>737</v>
+        <v>756</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01131</t>
+          <t>CM-26-01206</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Aalto Blanco</t>
+          <t>Beau-Séjour Bécot</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Aalto Bodegas y Viñedos</t>
+          <t>Château Beau-Séjour Bécot</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>769</v>
+        <v>2858</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>4'359.83</t>
+          <t>23'820.78</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0364</v>
+        <v>0.0187</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0054</v>
+        <v>0.0295</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>756</v>
+        <v>778</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01206</t>
+          <t>CM-26-01160</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2831,537 +2831,537 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Beau-Séjour Bécot</t>
+          <t>Châteauneuf du Pape</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Beau-Séjour Bécot</t>
+          <t>Clos des Papes</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2858</v>
+        <v>1631</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>23'820.78</t>
+          <t>15'338.87</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0187</v>
+        <v>0.0237</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0295</v>
+        <v>0.019</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.023</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>778</v>
+        <v>881</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01160</t>
+          <t>CM-26-01151</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape</t>
+          <t>Champagne Brut Dom Pérignon</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Clos des Papes</t>
+          <t>Dom Pérignon</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1631</v>
+        <v>984</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>15'338.87</t>
+          <t>12'917.47</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0237</v>
+        <v>0.0174</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0218</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>881</v>
+        <v>929</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01151</t>
+          <t>CM-26-01190</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Dom Pérignon</t>
+          <t>Garrus Rosé</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Dom Pérignon</t>
+          <t>Château d'Esclans</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>984</v>
+        <v>3376</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>12'917.47</t>
+          <t>12'745.67</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0174</v>
+        <v>0.0134</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.016</v>
+        <v>0.0158</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0168</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>929</v>
+        <v>955</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01190</t>
+          <t>CM-26-01166</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Garrus Rosé</t>
+          <t>L'Ermita</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château d'Esclans</t>
+          <t>Alvaro Palacios</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3376</v>
+        <v>457</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>12'745.67</t>
+          <t>8'709.95</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0134</v>
+        <v>0.0142</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0158</v>
+        <v>0.0108</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0144</v>
+        <v>0.0128</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01166</t>
+          <t>CM-26-01161</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>L'Ermita</t>
+          <t>Brunello di Montalcino Riserva</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Alvaro Palacios</t>
+          <t>Biondi Santi</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>457</v>
+        <v>1180</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>8'709.95</t>
+          <t>13'542.92</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.0073</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0108</v>
+        <v>0.0168</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0128</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>970</v>
+        <v>1013</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01161</t>
+          <t>CM-26-01188</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino Riserva</t>
+          <t>Cepparello</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Biondi Santi</t>
+          <t>Isole e Olena</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1180</v>
+        <v>2808</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>13'542.92</t>
+          <t>5'370.64</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0073</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0168</v>
+        <v>0.0067</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0111</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>1013</v>
+        <v>1033</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01188</t>
+          <t>CM-26-01196</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Cepparello</t>
+          <t>Trotanoy</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Isole e Olena</t>
+          <t>Château Trotanoy</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2808</v>
+        <v>1349</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>5'370.64</t>
+          <t>6'553.48</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0047</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0067</v>
+        <v>0.0081</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0077</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01196</t>
+          <t>CM-26-01165</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Trotanoy</t>
+          <t>Pavillon Blanc Second Vin</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Trotanoy</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1349</v>
+        <v>3510</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>6'553.48</t>
+          <t>4'412.30</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0047</v>
+        <v>0.0043</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0081</v>
+        <v>0.0055</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0061</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>1041</v>
+        <v>1151</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01165</t>
+          <t>CM-26-01211</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Pavillon Blanc Second Vin</t>
+          <t>Chambertin Clos de Bèze</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Domaine Armand Rousseau</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3510</v>
+        <v>107</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>4'412.30</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0055</v>
+        <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01211</t>
+          <t>CM-26-01209</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Chambertin Clos de Bèze</t>
+          <t>Chambertin</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
@@ -3417,11 +3417,11 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01209</t>
+          <t>CM-26-01208</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -3477,11 +3477,11 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01208</t>
+          <t>CM-26-01203</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
@@ -3537,11 +3537,11 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01203</t>
+          <t>CM-26-01179</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3551,26 +3551,26 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Chambertin</t>
+          <t>La Malvasia di Milano</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine Armand Rousseau</t>
+          <t>La Vigna di Leonardo</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
@@ -3595,68 +3595,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="n">
-        <v>1155</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01179</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>La Malvasia di Milano</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>La Vigna di Leonardo</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>359</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N27"/>
+  <autoFilter ref="A3:N26"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3700,7 +3640,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5261,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -6179,131 +6119,131 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-00966</t>
+          <t>CM-26-01022</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Dom Pérignon Rosé</t>
+          <t>Pétrus</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Dom Pérignon</t>
+          <t>Château Pétrus</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1195</v>
+        <v>566</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>57'068.01</t>
+          <t>65'929.06</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0396</v>
+        <v>0.0267</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0708</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0521</v>
+        <v>0.0487</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01022</t>
+          <t>CM-26-01066</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Pétrus</t>
+          <t>Galatrona</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Pétrus</t>
+          <t>Fattoria Petrolo</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>566</v>
+        <v>2984</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>65'929.06</t>
+          <t>46'947.63</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0267</v>
+        <v>0.0418</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0582</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0487</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01066</t>
+          <t>CM-26-01026</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -6313,7 +6253,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Galatrona</t>
+          <t>Corton</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -6323,47 +6263,47 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Fattoria Petrolo</t>
+          <t>Domaine Rapet Père &amp; Fils</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2984</v>
+        <v>3194</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>46'947.63</t>
+          <t>44'534.60</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0418</v>
+        <v>0.037</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0582</v>
+        <v>0.0552</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0484</v>
+        <v>0.0443</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-00971</t>
+          <t>CM-26-01097</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -6373,67 +6313,67 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Barolo Monfortino Riserva</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Giacomo Conterno</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>976</v>
+        <v>585</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>72'489.59</t>
+          <t>57'108.49</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0155</v>
+        <v>0.0258</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0708</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0453</v>
+        <v>0.0438</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>405</v>
+        <v>436</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01026</t>
+          <t>CM-26-01146</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Corton</t>
+          <t>Echezeaux</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -6443,47 +6383,47 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Rapet Père &amp; Fils</t>
+          <t>Mongeard Mugneret</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3194</v>
+        <v>1652</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>44'534.60</t>
+          <t>51'694.28</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0274</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0552</v>
+        <v>0.0641</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0443</v>
+        <v>0.0421</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01097</t>
+          <t>CM-26-01104</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -6493,17 +6433,17 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Harlan Estate</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -6512,38 +6452,38 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>585</v>
+        <v>669</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>57'108.49</t>
+          <t>60'905.73</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.0194</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.0755</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0438</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01146</t>
+          <t>CM-26-01150</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -6553,29 +6493,29 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Echezeaux</t>
+          <t>Lynch Bages</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Mongeard Mugneret</t>
+          <t>Château Lynch Bages</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1652</v>
+        <v>1896</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -6584,86 +6524,86 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>51'694.28</t>
+          <t>49'549.21</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
         <v>0.0274</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0641</v>
+        <v>0.0614</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0421</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01104</t>
+          <t>CM-26-01090</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Blanc de Blancs Dosaggio Zero</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Harlan Estate</t>
+          <t>Azienda Agricola Alessandra Divella</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>669</v>
+        <v>2344</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>60'905.73</t>
+          <t>26'400.15</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0194</v>
+        <v>0.045</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0755</v>
+        <v>0.0327</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0418</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01150</t>
+          <t>CM-26-01113</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -6673,7 +6613,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Lynch Bages</t>
+          <t>Hermitage La Chapelle</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -6683,47 +6623,47 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Lynch Bages</t>
+          <t>Domaine Paul Jaboulet Aîné</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1896</v>
+        <v>2206</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>49'549.21</t>
+          <t>48'374.15</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0274</v>
+        <v>0.0254</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0614</v>
+        <v>0.06</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.041</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01090</t>
+          <t>CM-26-01124</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -6733,7 +6673,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Blanc de Blancs Dosaggio Zero</t>
+          <t>Tertre Blanc</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -6743,158 +6683,158 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Azienda Agricola Alessandra Divella</t>
+          <t>Château du Tertre</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2344</v>
+        <v>822</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>26'400.15</t>
+          <t>7'004.52</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0577</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0327</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0401</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>474</v>
+        <v>502</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01113</t>
+          <t>CM-26-01021</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Hermitage La Chapelle</t>
+          <t>Vivaltus</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Domaine Paul Jaboulet Aîné</t>
+          <t>Bodega Vivaltus</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2206</v>
+        <v>2974</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>48'374.15</t>
+          <t>31'780.50</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0368</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.06</v>
+        <v>0.0394</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01124</t>
+          <t>CM-26-01192</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Tertre Blanc</t>
+          <t>Duclot 9 bottles Case Bordeaux Collection (1 x 75cl of each Petrus, Mouton, Lafite,Margaux,Haut Brion,Mission,Cheval ,Ausone,Yquem)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château du Tertre</t>
+          <t>Groupe Duclot</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>822</v>
+        <v>1174</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>7'004.52</t>
+          <t>63'981.51</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0577</v>
+        <v>0.0073</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0381</v>
+        <v>0.0361</v>
       </c>
     </row>
   </sheetData>
@@ -6942,7 +6882,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10003,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-14 10:40  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-04-14 17:13  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report.xlsx
+++ b/AVUwinnersCM/winners_report.xlsx
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9867,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:07  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report.xlsx
+++ b/AVUwinnersCM/winners_report.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 All-Time'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last 21 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Last Month (April 2026)'!$A$3:$N$53</definedName>
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2132,14 +2132,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 27 Apr 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 28 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2277,131 +2277,131 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>148</v>
+        <v>696</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01330</t>
+          <t>CM-26-01354</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Gaia &amp; Rey Chardonnay</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Gaja</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>407</v>
+        <v>49</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>47'219.26</t>
+          <t>2'438.36</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.09</v>
+        <v>0.0439</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.0585</v>
+        <v>0.003</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.0774</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>376</v>
+        <v>716</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01332</t>
+          <t>CM-26-01353</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Bòggina Bianco</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Fattoria Petrolo</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1792</v>
+        <v>63</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>22'161.78</t>
+          <t>11'782.68</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0614</v>
+        <v>0.0342</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0275</v>
+        <v>0.0146</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.0478</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>696</v>
+        <v>798</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01354</t>
+          <t>CM-26-01365</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -2411,127 +2411,127 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Sangiovese</t>
+          <t>Riesling Auslese Scharzhofberger Goldkapsel</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Case Basse - Gianfranco Soldera</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>49</v>
+        <v>496</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2'438.36</t>
+          <t>24'653.16</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0439</v>
+        <v>0.0174</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.003</v>
+        <v>0.0305</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.0275</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>716</v>
+        <v>899</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01353</t>
+          <t>CM-26-01393</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Sangiovese</t>
+          <t>Pontet Canet</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Case Basse - Gianfranco Soldera</t>
+          <t>Château Pontet Canet</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>11'782.68</t>
+          <t>897.26</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0342</v>
+        <v>0.0291</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.0011</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0264</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>798</v>
+        <v>944</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01365</t>
+          <t>CM-26-01367</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger Goldkapsel</t>
+          <t>Minuty 281 Rosé</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Minuty</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -2550,98 +2550,98 @@
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>496</v>
+        <v>1334</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>24'653.16</t>
+          <t>8'623.53</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0174</v>
+        <v>0.0194</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0305</v>
+        <v>0.0107</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0226</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>814</v>
+        <v>982</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01342</t>
+          <t>CM-26-01364</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape Vieilles Vignes</t>
+          <t>Minuty 281 Rosé</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Domaine de Marcoux</t>
+          <t>Château Minuty</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>481</v>
+        <v>898</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>5'734.85</t>
+          <t>4'314.05</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0314</v>
+        <v>0.0192</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0071</v>
+        <v>0.0053</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>893</v>
+        <v>1017</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01333</t>
+          <t>CM-26-01391</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -2651,197 +2651,189 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape Vieilles Vignes</t>
+          <t>Pontet Canet</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Domaine de Marcoux</t>
+          <t>Château Pontet Canet</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>584</v>
+        <v>5857</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>5'486.90</t>
+          <t>16'965.76</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0258</v>
+        <v>0.0043</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.0068</v>
+        <v>0.021</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0182</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>899</v>
+        <v>1204</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01393</t>
+          <t>CM-26-01351</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Pontet Canet</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Pontet Canet</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>897.26</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0291</v>
+        <v>0</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>944</v>
+        <v>1205</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01367</t>
+          <t>CM-26-01396</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Minuty 281 Rosé</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Château Minuty</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1334</v>
+        <v>833</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>8'623.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0194</v>
+        <v>0</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0107</v>
+        <v>0</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>982</v>
+        <v>1206</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01364</t>
+          <t>CM-26-01394</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Minuty 281 Rosé</t>
+          <t>Pontet Canet</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Minuty</t>
+          <t>Château Pontet Canet</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -2850,127 +2842,119 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>898</v>
+        <v>23</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>4'314.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0192</v>
+        <v>0</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0053</v>
+        <v>0</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>1017</v>
+        <v>1207</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01391</t>
+          <t>CM-26-01383</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Pontet Canet</t>
+          <t>Palmer</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Pontet Canet</t>
+          <t>Château Palmer</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>5857</v>
+        <v>460</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>16'965.76</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01351</t>
+          <t>CM-26-01381</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Sangiovese</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Case Basse - Gianfranco Soldera</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>149</v>
+        <v>5312</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>0</v>
@@ -2997,32 +2981,40 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01396</t>
+          <t>CM-26-01379</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>⚪</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
+          <t>Champagne Brut Belle Epoque</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Perrier-Jouët</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>833</v>
+        <v>1301</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
@@ -3049,40 +3041,40 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01394</t>
+          <t>CM-26-01360</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Pontet Canet</t>
+          <t>Axelle de Valandraud</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Pontet Canet</t>
+          <t>Château Valandraud</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>23</v>
+        <v>2174</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -3109,11 +3101,11 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01383</t>
+          <t>CM-26-01352</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -3123,26 +3115,26 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Palmer</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Palmer</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>460</v>
+        <v>80</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
@@ -3169,32 +3161,40 @@
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01381</t>
+          <t>CM-26-01345</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>⚪</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+          <t>Prosecco Brut Millesimato</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Villa Marcello</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>5312</v>
+        <v>806</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -3219,248 +3219,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>1209</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01379</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Champagne Brut Belle Epoque</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Perrier-Jouët</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1301</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>1210</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01360</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Axelle de Valandraud</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Château Valandraud</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>2174</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="n">
-        <v>1211</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01352</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Sangiovese</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Case Basse - Gianfranco Soldera</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>1212</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01345</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Prosecco Brut Millesimato</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Villa Marcello</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>806</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:N24"/>
+  <autoFilter ref="A3:N20"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3497,14 +3257,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 20 Apr 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 21 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -3762,21 +3522,21 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01256</t>
+          <t>CM-26-01330</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Gaia &amp; Rey Chardonnay</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -3786,187 +3546,187 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Spottswoode</t>
+          <t>Gaja</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3420</v>
+        <v>407</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>130'884.01</t>
+          <t>47'219.26</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0396</v>
+        <v>0.09</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1622</v>
+        <v>0.0585</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.0886</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01330</t>
+          <t>CM-26-01302</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Gaia &amp; Rey Chardonnay</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Gaja</t>
+          <t>Château Lafite Rothschild</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>407</v>
+        <v>777</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>47'219.26</t>
+          <t>117'808.49</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.09</v>
+        <v>0.0194</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0585</v>
+        <v>0.146</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0774</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>181</v>
+        <v>239</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01302</t>
+          <t>CM-26-01282</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Champagne Brut Cristal</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Louis Roederer</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>777</v>
+        <v>2546</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>117'808.49</t>
+          <t>84'326.26</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.0194</v>
+        <v>0.0347</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.146</v>
+        <v>0.1045</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0626</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>239</v>
+        <v>344</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01282</t>
+          <t>CM-26-01289</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Cristal</t>
+          <t>Haut Brion</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Louis Roederer</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -3975,98 +3735,98 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2546</v>
+        <v>868</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>84'326.26</t>
+          <t>81'799.39</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.0174</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1045</v>
+        <v>0.1013</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0626</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01289</t>
+          <t>CM-26-01306</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion</t>
+          <t>Family and Friends</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Feudo Maccari</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>868</v>
+        <v>2492</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>81'799.39</t>
+          <t>27'067.91</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0174</v>
+        <v>0.0597</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1013</v>
+        <v>0.0335</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.051</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01306</t>
+          <t>CM-26-01332</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4076,127 +3836,127 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Family and Friends</t>
+          <t>Bòggina Bianco</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Feudo Maccari</t>
+          <t>Fattoria Petrolo</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2492</v>
+        <v>1792</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>27'067.91</t>
+          <t>22'161.78</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0597</v>
+        <v>0.0614</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0335</v>
+        <v>0.0275</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0492</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>371</v>
+        <v>477</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01263</t>
+          <t>CM-26-01305</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Stella Solare</t>
+          <t>Larcis Ducasse</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Croix de Labrie</t>
+          <t>Château Larcis Ducasse</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1115</v>
+        <v>2198</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>15'707.45</t>
+          <t>35'344.45</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0392</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0195</v>
+        <v>0.0438</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0484</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>376</v>
+        <v>539</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01332</t>
+          <t>CM-26-01297</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Bòggina Bianco</t>
+          <t>Oreno</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -4206,407 +3966,407 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Fattoria Petrolo</t>
+          <t>Tenuta Sette Ponti</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1792</v>
+        <v>2359</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>22'161.78</t>
+          <t>25'111.44</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0614</v>
+        <v>0.0403</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0275</v>
+        <v>0.0311</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0478</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>477</v>
+        <v>562</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01305</t>
+          <t>CM-26-01318</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Larcis Ducasse</t>
+          <t>Único Reserva Especial Venta 2026 (2011+2012+2014)</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Larcis Ducasse</t>
+          <t>Bodegas Vega Sicilia</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2198</v>
+        <v>1736</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>35'344.45</t>
+          <t>44'810.48</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0392</v>
+        <v>0.0211</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0438</v>
+        <v>0.0555</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.041</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>539</v>
+        <v>612</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01297</t>
+          <t>CM-26-01321</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Oreno</t>
+          <t>Champagne Brut 7 Crus</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Tenuta Sette Ponti</t>
+          <t>Agrapart &amp; Fils</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2359</v>
+        <v>1065</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>25'111.44</t>
+          <t>10'605.80</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0403</v>
+        <v>0.0446</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0311</v>
+        <v>0.0131</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0366</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>562</v>
+        <v>696</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01318</t>
+          <t>CM-26-01354</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Único Reserva Especial Venta 2026 (2011+2012+2014)</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Bodegas Vega Sicilia</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1736</v>
+        <v>49</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>44'810.48</t>
+          <t>2'438.36</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0211</v>
+        <v>0.0439</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0555</v>
+        <v>0.003</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0349</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>612</v>
+        <v>716</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01321</t>
+          <t>CM-26-01353</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut 7 Crus</t>
+          <t>Sangiovese</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Agrapart &amp; Fils</t>
+          <t>Case Basse - Gianfranco Soldera</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1065</v>
+        <v>63</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>10'605.80</t>
+          <t>11'782.68</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0446</v>
+        <v>0.0342</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0131</v>
+        <v>0.0146</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.032</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>664</v>
+        <v>766</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01247</t>
+          <t>CM-26-01304</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Baronarques Blanc</t>
+          <t>Belvedere</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Domaine de Baronarques</t>
+          <t>Castello Luigi</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2960</v>
+        <v>3071</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>14'141.51</t>
+          <t>19'883.46</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.037</v>
+        <v>0.0239</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0175</v>
+        <v>0.0246</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0292</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>696</v>
+        <v>769</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01354</t>
+          <t>CM-26-01275</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Sangiovese</t>
+          <t>Brunello di Montalcino</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Case Basse - Gianfranco Soldera</t>
+          <t>Biondi Santi</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>49</v>
+        <v>2693</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2'438.36</t>
+          <t>34'153.87</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0439</v>
+        <v>0.0121</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.003</v>
+        <v>0.0423</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0275</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>716</v>
+        <v>798</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01353</t>
+          <t>CM-26-01365</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -4616,57 +4376,57 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Sangiovese</t>
+          <t>Riesling Auslese Scharzhofberger Goldkapsel</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Case Basse - Gianfranco Soldera</t>
+          <t>Egon Müller Scharzhof</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>63</v>
+        <v>496</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>11'782.68</t>
+          <t>24'653.16</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0342</v>
+        <v>0.0174</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0146</v>
+        <v>0.0305</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0264</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>766</v>
+        <v>814</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01304</t>
+          <t>CM-26-01342</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -4676,127 +4436,127 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Belvedere</t>
+          <t>Châteauneuf du Pape Vieilles Vignes</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Castello Luigi</t>
+          <t>Domaine de Marcoux</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3071</v>
+        <v>481</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>19'883.46</t>
+          <t>5'734.85</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0239</v>
+        <v>0.0314</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0246</v>
+        <v>0.0071</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0242</v>
+        <v>0.0217</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>769</v>
+        <v>893</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01275</t>
+          <t>CM-26-01333</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Brunello di Montalcino</t>
+          <t>Châteauneuf du Pape Vieilles Vignes</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Biondi Santi</t>
+          <t>Domaine de Marcoux</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2693</v>
+        <v>584</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>34'153.87</t>
+          <t>5'486.90</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0121</v>
+        <v>0.0258</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0423</v>
+        <v>0.0068</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0242</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>798</v>
+        <v>899</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01365</t>
+          <t>CM-26-01393</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Riesling Auslese Scharzhofberger Goldkapsel</t>
+          <t>Pontet Canet</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -4806,7 +4566,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Egon Müller Scharzhof</t>
+          <t>Château Pontet Canet</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -4815,218 +4575,218 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>496</v>
+        <v>74</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>24'653.16</t>
+          <t>897.26</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0174</v>
+        <v>0.0291</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0305</v>
+        <v>0.0011</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0226</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>814</v>
+        <v>944</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01342</t>
+          <t>CM-26-01367</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape Vieilles Vignes</t>
+          <t>Minuty 281 Rosé</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Domaine de Marcoux</t>
+          <t>Château Minuty</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>481</v>
+        <v>1334</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>5'734.85</t>
+          <t>8'623.53</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0314</v>
+        <v>0.0194</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0071</v>
+        <v>0.0107</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0217</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>893</v>
+        <v>962</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01333</t>
+          <t>CM-26-01316</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Châteauneuf du Pape Vieilles Vignes</t>
+          <t>Macan</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Domaine de Marcoux</t>
+          <t>Rothschild/Vega Sicilia</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>584</v>
+        <v>3001</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>5'486.90</t>
+          <t>10'468.00</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.0157</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0068</v>
+        <v>0.013</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0182</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>895</v>
+        <v>982</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01269</t>
+          <t>CM-26-01364</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Barbaresco Asili Riserva</t>
+          <t>Minuty 281 Rosé</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Azienda Agricola Falletto di Bruno Giacosa</t>
+          <t>Château Minuty</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1304</v>
+        <v>898</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>24'290.88</t>
+          <t>4'314.05</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0192</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0301</v>
+        <v>0.0053</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.018</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>899</v>
+        <v>1017</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01393</t>
+          <t>CM-26-01391</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -5055,29 +4815,29 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>74</v>
+        <v>5857</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>897.26</t>
+          <t>16'965.76</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0291</v>
+        <v>0.0043</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0011</v>
+        <v>0.021</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0179</v>
+        <v>0.011</v>
       </c>
     </row>
   </sheetData>
@@ -5118,14 +4878,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 13 Apr 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 14 Apr 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -6583,71 +6343,71 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>590</v>
+        <v>612</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01206</t>
+          <t>CM-26-01321</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Beau-Séjour Bécot</t>
+          <t>Champagne Brut 7 Crus</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Beau-Séjour Bécot</t>
+          <t>Agrapart &amp; Fils</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2858</v>
+        <v>1065</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>32'961.78</t>
+          <t>10'605.80</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0286</v>
+        <v>0.0446</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0408</v>
+        <v>0.0131</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0335</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>612</v>
+        <v>664</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01321</t>
+          <t>CM-26-01247</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -6657,48 +6417,48 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut 7 Crus</t>
+          <t>Baronarques Blanc</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Agrapart &amp; Fils</t>
+          <t>Domaine de Baronarques</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1065</v>
+        <v>2960</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>10'605.80</t>
+          <t>14'141.51</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0446</v>
+        <v>0.037</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0131</v>
+        <v>0.0175</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.032</v>
+        <v>0.0292</v>
       </c>
     </row>
   </sheetData>
@@ -6746,7 +6506,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9627,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-04 09:25  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-05-05 16:33  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report.xlsx
+++ b/AVUwinnersCM/winners_report.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 All-Time'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last 21 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Last Month (May 2026)'!$A$3:$N$53</definedName>
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:57  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2132,14 +2132,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 03 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 08 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:57  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2217,71 +2217,71 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>8</v>
+        <v>982</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01713</t>
+          <t>CM-26-01778</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Champagne Brut Grande Cuvée</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Krug</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>80</v>
+        <v>703</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>22.50%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>89'655.03</t>
+          <t>17'154.02</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.4704</v>
+        <v>0.0148</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.111</v>
+        <v>0.0212</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.3266</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>96</v>
+        <v>1107</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01761</t>
+          <t>CM-26-01789</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -2291,127 +2291,127 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>32</v>
+        <v>509</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>2</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>48'468.66</t>
+          <t>11'937.82</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.1307</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.06</v>
+        <v>0.0148</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1024</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>251</v>
+        <v>1205</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01787</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>San Leonardo</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Tenuta San Leonardo</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1862</v>
+        <v>2115</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>111'433.62</t>
+          <t>356.30</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.138</v>
+        <v>0.0004</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.0606</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>302</v>
+        <v>1293</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01786</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -2421,57 +2421,57 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>5146</v>
+        <v>418</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>96'159.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0142</v>
+        <v>0</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1191</v>
+        <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.0562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>360</v>
+        <v>1318</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01788</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2481,57 +2481,57 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3866</v>
+        <v>532</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>59'543.87</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0351</v>
+        <v>0</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0737</v>
+        <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>426</v>
+        <v>1319</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01720</t>
+          <t>CM-26-01785</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Trottevieille</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2541,47 +2541,47 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Trottevieille</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>707</v>
+        <v>461</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>10'973.28</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0136</v>
+        <v>0</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>602</v>
+        <v>1320</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01714</t>
+          <t>CM-26-01782</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2601,986 +2601,102 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>401</v>
+        <v>23</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>18'986.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0418</v>
+        <v>0</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0235</v>
+        <v>0</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>732</v>
+        <v>1321</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01716</t>
+          <t>CM-26-01771</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Léoville Poyferré</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Poyferré</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>605</v>
+        <v>514</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>23'090.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0276</v>
+        <v>0</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.0286</v>
+        <v>0</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>747</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01715</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Château Mouton Rothschild</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>439</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>1.59%</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>15'102.94</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0.0187</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0.0274</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>982</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01778</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Champagne Brut Grande Cuvée</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Krug</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>703</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>17'154.02</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0.0212</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0.0174</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>1101</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01717</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Château Mouton Rothschild</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1326</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>0.45%</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>11'780.82</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0.0094</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0.0115</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>1105</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01726</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>🩷</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Beychevelle</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Château Beychevelle</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>0.85%</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>881.02</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0.0178</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0.0111</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>1107</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01789</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Champagne le Mesnil</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Maison Salon</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>509</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>11'937.82</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0.008200000000000001</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0.0108</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>1195</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01718</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Château Mouton Rothschild</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>431</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>2'304.18</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>1205</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01787</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>🩷</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>San Leonardo</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Tenuta San Leonardo</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>2115</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>0.05%</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>356.30</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>0.0008</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="n">
-        <v>1293</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01786</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>418</v>
-      </c>
-      <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>1318</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01788</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>532</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>1319</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01785</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>461</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01782</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="n">
-        <v>1321</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01771</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Champagne le Mesnil</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Maison Salon</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>514</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>1322</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01760</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>975</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="6" t="n">
-        <v>1323</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01756</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>5248</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>1324</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01734</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>🩷</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Les Carmes Haut Brion</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Château Les Carmes Haut-Brion</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N26"/>
+  <autoFilter ref="A3:N11"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3617,14 +2733,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 27 May 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 01 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:57  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -3822,21 +2938,21 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01641</t>
+          <t>CM-26-01711</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Trotanoy</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3846,177 +2962,177 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Château Trotanoy</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>17.65%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>17'219.32</t>
+          <t>459.98</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.369</v>
+        <v>0.19</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2299</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01656</t>
+          <t>CM-26-01695</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Montevertine</t>
+          <t>Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Montevertine</t>
+          <t>Château Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
+        <v>495</v>
+      </c>
+      <c r="I7" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>6</v>
-      </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>15.79%</t>
+          <t>7.68%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>17'218.49</t>
+          <t>21'418.67</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.3301</v>
+        <v>0.1606</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0265</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2066</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01711</t>
+          <t>CM-26-01761</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>459.98</t>
+          <t>48'468.66</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.19</v>
+        <v>0.1307</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1142</v>
+        <v>0.1024</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01695</t>
+          <t>CM-26-01698</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Grand Puy Lacoste</t>
+          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4026,107 +3142,107 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Grand Puy Lacoste</t>
+          <t>Château La Mission Haut Brion</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>495</v>
+        <v>3950</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>7.68%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>21'418.67</t>
+          <t>141'031.82</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1606</v>
+        <v>0.0222</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0265</v>
+        <v>0.1746</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.107</v>
+        <v>0.0832</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01761</t>
+          <t>CM-26-01701</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Reserve de la Comtesse (2nd Vin)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Pichon-Longueville Comtesse de Lalande</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>32</v>
+        <v>3667</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>48'468.66</t>
+          <t>121'427.44</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1307</v>
+        <v>0.0291</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.06</v>
+        <v>0.1503</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1024</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>137</v>
+        <v>244</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01698</t>
+          <t>CM-26-01697</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -4136,7 +3252,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
+          <t>Pavie</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -4146,7 +3262,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Château Pavie</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -4155,158 +3271,158 @@
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3950</v>
+        <v>2842</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>141'031.82</t>
+          <t>89'670.37</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0222</v>
+        <v>0.028</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1746</v>
+        <v>0.111</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0832</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01701</t>
+          <t>CM-26-01750</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Reserve de la Comtesse (2nd Vin)</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Pichon-Longueville Comtesse de Lalande</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3667</v>
+        <v>1862</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>121'427.44</t>
+          <t>111'433.62</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0291</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1503</v>
+        <v>0.138</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0776</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>152</v>
+        <v>290</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01679</t>
+          <t>CM-26-01705</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>La Mission Haut-Brion</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2342</v>
+        <v>4119</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>138'853.14</t>
+          <t>67'692.38</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0391</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.1719</v>
+        <v>0.0838</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>232</v>
+        <v>302</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01646</t>
+          <t>CM-26-01738</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4316,67 +3432,67 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Éphémère 030</t>
+          <t>Les Carmes Haut Brion</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Drémont &amp; Savart</t>
+          <t>Château Les Carmes Haut-Brion</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>938</v>
+        <v>5146</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>20'179.93</t>
+          <t>96'159.60</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0891</v>
+        <v>0.0142</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.025</v>
+        <v>0.1191</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0635</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>244</v>
+        <v>323</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01697</t>
+          <t>CM-26-01708</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Brane Cantenac</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -4386,117 +3502,117 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Pavie</t>
+          <t>Château Brane Cantenac</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2842</v>
+        <v>1480</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>89'670.37</t>
+          <t>24'790.36</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.028</v>
+        <v>0.0707</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.111</v>
+        <v>0.0307</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0612</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>251</v>
+        <v>360</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01749</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1862</v>
+        <v>3866</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>111'433.62</t>
+          <t>59'543.87</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0351</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.138</v>
+        <v>0.0737</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0606</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>290</v>
+        <v>426</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01705</t>
+          <t>CM-26-01720</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Trottevieille</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -4506,117 +3622,117 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Trottevieille</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>4119</v>
+        <v>707</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>67'692.38</t>
+          <t>10'973.28</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0391</v>
+        <v>0.065</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0838</v>
+        <v>0.0136</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.057</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>302</v>
+        <v>583</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01704</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>Sloan Red</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>5146</v>
+        <v>332</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>96'159.60</t>
+          <t>26'070.11</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.0378</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1191</v>
+        <v>0.0323</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0562</v>
+        <v>0.0356</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>323</v>
+        <v>602</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01708</t>
+          <t>CM-26-01714</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Brane Cantenac</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -4626,7 +3742,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Brane Cantenac</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -4635,108 +3751,108 @@
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1480</v>
+        <v>401</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>24'790.36</t>
+          <t>18'986.65</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0707</v>
+        <v>0.0418</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0307</v>
+        <v>0.0235</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0547</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>360</v>
+        <v>732</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01716</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Léoville Poyferré</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Léoville Poyferré</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3866</v>
+        <v>605</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>59'543.87</t>
+          <t>23'090.54</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0351</v>
+        <v>0.0276</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0737</v>
+        <v>0.0286</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>361</v>
+        <v>739</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01676</t>
+          <t>CM-26-01699</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Corton-Charlemagne</t>
+          <t>Family and Friends Firraru</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -4746,347 +3862,347 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Domaine Rapet Père &amp; Fils</t>
+          <t>Feudo Maccari</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1923</v>
+        <v>898</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>60'048.98</t>
+          <t>5'313.11</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0347</v>
+        <v>0.0418</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0743</v>
+        <v>0.0066</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0505</v>
+        <v>0.0277</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>375</v>
+        <v>747</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01674</t>
+          <t>CM-26-01715</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Cabernet Sauvignon</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Screaming Eagle Winery</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>558</v>
+        <v>439</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>75'668.55</t>
+          <t>15'102.94</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0188</v>
+        <v>0.0332</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0187</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0488</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>426</v>
+        <v>876</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01720</t>
+          <t>CM-26-01694</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Trottevieille</t>
+          <t>Promontory</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Château Trottevieille</t>
+          <t>Promontory</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>707</v>
+        <v>238</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>10'973.28</t>
+          <t>11'589.97</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.065</v>
+        <v>0.0263</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0136</v>
+        <v>0.0144</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0444</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>498</v>
+        <v>908</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01639</t>
+          <t>CM-26-01683</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Palmer</t>
+          <t>Giscours</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Château Palmer</t>
+          <t>Château Giscours</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2498</v>
+        <v>2609</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>71'984.09</t>
+          <t>12'874.12</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0232</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0891</v>
+        <v>0.0159</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0407</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>502</v>
+        <v>938</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01647</t>
+          <t>CM-26-01685</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Cheval des Andes</t>
+          <t>Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Cheval des Andes</t>
+          <t>Château Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>257</v>
+        <v>2221</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>3'284.98</t>
+          <t>13'547.97</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.065</v>
+        <v>0.0207</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0041</v>
+        <v>0.0168</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0406</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>527</v>
+        <v>982</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01652</t>
+          <t>CM-26-01778</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Galatrona</t>
+          <t>Champagne Brut Grande Cuvée</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Fattoria Petrolo</t>
+          <t>Krug</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3049</v>
+        <v>703</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>40'374.07</t>
+          <t>17'154.02</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0316</v>
+        <v>0.0148</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0212</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.039</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>583</v>
+        <v>1033</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01704</t>
+          <t>CM-26-01684</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -5096,77 +4212,77 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Sloan Red</t>
+          <t>Champagne Brut Cristal Rosé</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Louis Roederer</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>332</v>
+        <v>769</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>26'070.11</t>
+          <t>14'036.89</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0378</v>
+        <v>0.0136</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0323</v>
+        <v>0.0174</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0356</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>602</v>
+        <v>1035</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01714</t>
+          <t>CM-26-01710</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Champagne Brut R Vintage</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Maison Ruinart</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -5175,29 +4291,29 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>401</v>
+        <v>1276</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>18'986.65</t>
+          <t>6'347.58</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0418</v>
+        <v>0.0197</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0235</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.015</v>
       </c>
     </row>
   </sheetData>
@@ -5238,14 +4354,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 20 May 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 25 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:57  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -5323,11 +4439,11 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01574</t>
+          <t>CM-26-01713</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5337,7 +4453,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Carruades de Lafite Rothschild (2nd Vin)</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -5347,47 +4463,47 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>47.83%</t>
+          <t>22.50%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>36'059.70</t>
+          <t>89'655.03</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1</v>
+        <v>0.4704</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.0446</v>
+        <v>0.111</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.6178</v>
+        <v>0.3266</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01713</t>
+          <t>CM-26-01706</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -5416,48 +4532,48 @@
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>80</v>
+        <v>3482</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>22.50%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>89'655.03</t>
+          <t>461'783.14</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.4704</v>
+        <v>0.0498</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.111</v>
+        <v>0.5718</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.3266</v>
+        <v>0.2586</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01706</t>
+          <t>CM-26-01641</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Trotanoy</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -5467,47 +4583,47 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Trotanoy</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3482</v>
+        <v>51</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>17.65%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>461'783.14</t>
+          <t>17'219.32</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0498</v>
+        <v>0.369</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.5718</v>
+        <v>0.0213</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2586</v>
+        <v>0.2299</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01641</t>
+          <t>CM-26-01656</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -5517,127 +4633,127 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Trotanoy</t>
+          <t>Montevertine</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Trotanoy</t>
+          <t>Montevertine</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>17.65%</t>
+          <t>15.79%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>17'219.32</t>
+          <t>17'218.49</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.369</v>
+        <v>0.3301</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>0.0213</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2299</v>
+        <v>0.2066</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01656</t>
+          <t>CM-26-01711</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Montevertine</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Montevertine</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>15.79%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>17'218.49</t>
+          <t>459.98</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3301</v>
+        <v>0.19</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2066</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01577</t>
+          <t>CM-26-01695</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Carillon de l'Angélus (2nd Vin)</t>
+          <t>Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -5647,107 +4763,107 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Angélus</t>
+          <t>Château Grand Puy Lacoste</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3203</v>
+        <v>495</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>7.68%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>237'861.60</t>
+          <t>21'418.67</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.028</v>
+        <v>0.1606</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.2945</v>
+        <v>0.0265</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1346</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01711</t>
+          <t>CM-26-01761</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>459.98</t>
+          <t>48'468.66</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.19</v>
+        <v>0.1307</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1142</v>
+        <v>0.1024</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01695</t>
+          <t>CM-26-01635</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -5757,297 +4873,297 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Grand Puy Lacoste</t>
+          <t>Le Serre Nuove dell'Ornellaia</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Grand Puy Lacoste</t>
+          <t>Tenuta dell'Ornellaia</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>495</v>
+        <v>283</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>7.68%</t>
+          <t>6.71%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>21'418.67</t>
+          <t>7'981.81</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1606</v>
+        <v>0.1403</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.0265</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.107</v>
+        <v>0.0881</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01567</t>
+          <t>CM-26-01698</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Lodovico</t>
+          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Tenuta di Biserno</t>
+          <t>Château La Mission Haut Brion</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>203</v>
+        <v>3950</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>7.39%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>23'081.35</t>
+          <t>141'031.82</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1545</v>
+        <v>0.0222</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0286</v>
+        <v>0.1746</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1041</v>
+        <v>0.0832</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01761</t>
+          <t>CM-26-01701</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Reserve de la Comtesse (2nd Vin)</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Pichon-Longueville Comtesse de Lalande</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>32</v>
+        <v>3667</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>48'468.66</t>
+          <t>121'427.44</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1307</v>
+        <v>0.0291</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.06</v>
+        <v>0.1503</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1024</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01635</t>
+          <t>CM-26-01679</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Le Serre Nuove dell'Ornellaia</t>
+          <t>La Mission Haut-Brion</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Tenuta dell'Ornellaia</t>
+          <t>Château La Mission Haut Brion</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>283</v>
+        <v>2342</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>6.71%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>7'981.81</t>
+          <t>138'853.14</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1403</v>
+        <v>0.0142</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.1719</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0881</v>
+        <v>0.07729999999999999</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>125</v>
+        <v>232</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01564</t>
+          <t>CM-26-01646</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Hermitage La Chapelle</t>
+          <t>Champagne Extra Brut Éphémère 030</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Domaine Paul Jaboulet Aîné</t>
+          <t>Drémont &amp; Savart</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2628</v>
+        <v>938</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>4.26%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>85'987.35</t>
+          <t>20'179.93</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0891</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.1065</v>
+        <v>0.025</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0635</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>137</v>
+        <v>244</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01698</t>
+          <t>CM-26-01697</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -6057,7 +5173,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
+          <t>Pavie</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -6067,7 +5183,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Château Pavie</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -6076,158 +5192,158 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3950</v>
+        <v>2842</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>141'031.82</t>
+          <t>89'670.37</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0222</v>
+        <v>0.028</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1746</v>
+        <v>0.111</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0832</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01701</t>
+          <t>CM-26-01750</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Reserve de la Comtesse (2nd Vin)</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château Pichon-Longueville Comtesse de Lalande</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3667</v>
+        <v>1862</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>121'427.44</t>
+          <t>111'433.62</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0291</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1503</v>
+        <v>0.138</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0776</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>152</v>
+        <v>271</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01679</t>
+          <t>CM-26-01624</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>La Mission Haut-Brion</t>
+          <t>Lafleur</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Château Lafleur</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2342</v>
+        <v>52</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>3.85%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>138'853.14</t>
+          <t>20'164.81</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.0805</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1719</v>
+        <v>0.025</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>176</v>
+        <v>290</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01575</t>
+          <t>CM-26-01705</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -6237,7 +5353,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Les Ormes de Pez</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -6247,47 +5363,47 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Les Ormes de Pez</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3188</v>
+        <v>4119</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>83'446.96</t>
+          <t>67'692.38</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0491</v>
+        <v>0.0391</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1033</v>
+        <v>0.0838</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0708</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>232</v>
+        <v>302</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01646</t>
+          <t>CM-26-01738</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -6297,67 +5413,67 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Champagne Extra Brut Éphémère 030</t>
+          <t>Les Carmes Haut Brion</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Drémont &amp; Savart</t>
+          <t>Château Les Carmes Haut-Brion</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>938</v>
+        <v>5146</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>20'179.93</t>
+          <t>96'159.60</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0891</v>
+        <v>0.0142</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.025</v>
+        <v>0.1191</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0635</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>244</v>
+        <v>323</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01697</t>
+          <t>CM-26-01708</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Brane Cantenac</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -6367,287 +5483,287 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Pavie</t>
+          <t>Château Brane Cantenac</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2842</v>
+        <v>1480</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>89'670.37</t>
+          <t>24'790.36</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.028</v>
+        <v>0.0707</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.111</v>
+        <v>0.0307</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0612</v>
+        <v>0.0547</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>251</v>
+        <v>360</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01749</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1862</v>
+        <v>3866</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>111'433.62</t>
+          <t>59'543.87</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0351</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.138</v>
+        <v>0.0737</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0606</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>271</v>
+        <v>361</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01624</t>
+          <t>CM-26-01676</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Lafleur</t>
+          <t>Corton-Charlemagne</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Château Lafleur</t>
+          <t>Domaine Rapet Père &amp; Fils</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>52</v>
+        <v>1923</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>20'164.81</t>
+          <t>60'048.98</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0805</v>
+        <v>0.0347</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.025</v>
+        <v>0.0743</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0583</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>290</v>
+        <v>371</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01705</t>
+          <t>CM-26-01633</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Ducru Beaucaillou</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Ducru Beaucaillou</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4119</v>
+        <v>1055</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>67'692.38</t>
+          <t>41'812.62</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0391</v>
+        <v>0.0475</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0838</v>
+        <v>0.0518</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.057</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>301</v>
+        <v>375</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01590</t>
+          <t>CM-26-01674</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Palmer</t>
+          <t>Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Palmer</t>
+          <t>Screaming Eagle Winery</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2657</v>
+        <v>558</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>80'925.55</t>
+          <t>75'668.55</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0268</v>
+        <v>0.0188</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.1002</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0562</v>
+        <v>0.0488</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01594</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -6657,127 +5773,127 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>Clos Apalta</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Lapostolle Winery</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5146</v>
+        <v>5530</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>96'159.60</t>
+          <t>64'545.20</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0142</v>
+        <v>0.0276</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1191</v>
+        <v>0.0799</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0562</v>
+        <v>0.0485</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>323</v>
+        <v>419</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01708</t>
+          <t>CM-26-01638</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Brane Cantenac</t>
+          <t>Cheval des Andes</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Brane Cantenac</t>
+          <t>Cheval des Andes</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1480</v>
+        <v>3870</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>24'790.36</t>
+          <t>46'484.89</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0707</v>
+        <v>0.0362</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0307</v>
+        <v>0.0576</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0547</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>360</v>
+        <v>426</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01720</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Trottevieille</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -6787,38 +5903,38 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Trottevieille</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3866</v>
+        <v>707</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>59'543.87</t>
+          <t>10'973.28</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0351</v>
+        <v>0.065</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0737</v>
+        <v>0.0136</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0505</v>
+        <v>0.0444</v>
       </c>
     </row>
   </sheetData>
@@ -6866,7 +5982,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:57  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9103,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-10 15:57  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-15 09:05  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report.xlsx
+++ b/AVUwinnersCM/winners_report.xlsx
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2132,14 +2132,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 15 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 16 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2757,91 +2757,91 @@
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>1058</v>
+        <v>1098</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01847</t>
+          <t>CM-26-01909</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Aalto</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Aalto Bodegas y Viñedos</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1664</v>
+        <v>1119</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>7'074.83</t>
+          <t>10'753.00</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0129</v>
+        <v>0.0058</v>
       </c>
       <c r="M13" s="6" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="N13" s="6" t="n">
         <v>0.008800000000000001</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0.0113</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01909</t>
+          <t>CM-26-01894</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -2850,38 +2850,38 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1119</v>
+        <v>160</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>10'753.00</t>
+          <t>963.07</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0058</v>
+        <v>0.0136</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0133</v>
+        <v>0.0012</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>1101</v>
+        <v>1126</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01894</t>
+          <t>CM-26-01895</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -2910,48 +2910,48 @@
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>160</v>
+        <v>3616</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>963.07</t>
+          <t>7'002.23</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0136</v>
+        <v>0.0054</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0012</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0086</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>1126</v>
+        <v>1141</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01895</t>
+          <t>CM-26-01940</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Ygrec de Ch. d'Yquem</t>
+          <t>Almaviva</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -2961,67 +2961,67 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château d'Yquem</t>
+          <t>Baron Philippe de Rothschild and Concha Y Toro</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3616</v>
+        <v>3416</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>7'002.23</t>
+          <t>4'668.32</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0054</v>
+        <v>0.0043</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0067</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>1141</v>
+        <v>1273</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01940</t>
+          <t>CM-26-01925</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Almaviva</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Baron Philippe de Rothschild and Concha Y Toro</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -3030,38 +3030,38 @@
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3416</v>
+        <v>134</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>4'668.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0043</v>
+        <v>0</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01925</t>
+          <t>CM-26-01922</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -3086,11 +3086,11 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>0</v>
@@ -3117,40 +3117,32 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01922</t>
+          <t>CM-26-01896</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>DRC Romanée St. Vivant</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
@@ -3177,11 +3169,11 @@
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01896</t>
+          <t>CM-26-01890</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3202,7 +3194,7 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>0</v>
@@ -3229,11 +3221,11 @@
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01890</t>
+          <t>CM-26-01889</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -3250,7 +3242,7 @@
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
@@ -3281,11 +3273,11 @@
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01889</t>
+          <t>CM-26-01888</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -3306,7 +3298,7 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>0</v>
@@ -3333,11 +3325,11 @@
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01888</t>
+          <t>CM-26-01884</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -3358,7 +3350,7 @@
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>12</v>
+        <v>257</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
@@ -3385,11 +3377,11 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01884</t>
+          <t>CM-26-01882</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -3410,7 +3402,7 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>257</v>
+        <v>33</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>0</v>
@@ -3437,11 +3429,11 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01882</t>
+          <t>CM-26-01881</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -3462,7 +3454,7 @@
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
@@ -3489,11 +3481,11 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01881</t>
+          <t>CM-26-01880</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3514,7 +3506,7 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>0</v>
@@ -3541,11 +3533,11 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01880</t>
+          <t>CM-26-01879</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -3566,7 +3558,7 @@
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
@@ -3593,11 +3585,11 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01879</t>
+          <t>CM-26-01877</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -3618,7 +3610,7 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>55</v>
+        <v>191</v>
       </c>
       <c r="I28" s="4" t="n">
         <v>0</v>
@@ -3681,14 +3673,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 08 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 09 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -4126,131 +4118,131 @@
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01778</t>
+          <t>CM-26-01843</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Grande Cuvée</t>
+          <t>Grands Echézeaux</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Krug</t>
+          <t>Mongeard Mugneret</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>703</v>
+        <v>2297</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>35'222.13</t>
+          <t>58'066.22</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0459</v>
+        <v>0.0243</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0436</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0433</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>437</v>
+        <v>489</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01843</t>
+          <t>CM-26-01945</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Grands Echézeaux</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Mongeard Mugneret</t>
+          <t>Château Lafite Rothschild</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>2297</v>
+        <v>1175</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>58'066.22</t>
+          <t>72'662.43</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0243</v>
+        <v>0.0073</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0433</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>489</v>
+        <v>583</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01945</t>
+          <t>CM-26-01789</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -4260,117 +4252,117 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1175</v>
+        <v>509</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>72'662.43</t>
+          <t>38'932.73</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0073</v>
+        <v>0.0254</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.09</v>
+        <v>0.0482</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0404</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>583</v>
+        <v>693</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01789</t>
+          <t>CM-26-01907</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>509</v>
+        <v>940</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>38'932.73</t>
+          <t>23'816.30</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0276</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0482</v>
+        <v>0.0295</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0345</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>693</v>
+        <v>750</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01907</t>
+          <t>CM-26-01912</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4380,307 +4372,307 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Meursault Perrières</t>
+          <t>Léoville Las Cases</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ballot-Millot</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>940</v>
+        <v>2662</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>23'816.30</t>
+          <t>36'543.63</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0276</v>
+        <v>0.0129</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0295</v>
+        <v>0.0452</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0284</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>750</v>
+        <v>826</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01912</t>
+          <t>CM-26-01935</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Léoville Las Cases</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2662</v>
+        <v>138</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>36'543.63</t>
+          <t>26'352.00</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0129</v>
+        <v>0.0155</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0452</v>
+        <v>0.0326</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0258</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>826</v>
+        <v>853</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01935</t>
+          <t>CM-26-01787</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>San Leonardo</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Tenuta San Leonardo</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>138</v>
+        <v>2115</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>26'352.00</t>
+          <t>16'195.97</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0155</v>
+        <v>0.0213</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0326</v>
+        <v>0.0201</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0223</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01787</t>
+          <t>CM-26-01825</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>San Leonardo</t>
+          <t>Cuvée Etoile Rosé</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Tenuta San Leonardo</t>
+          <t>Domaine Ott</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2115</v>
+        <v>2762</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>16'195.97</t>
+          <t>16'897.97</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0213</v>
+        <v>0.0202</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0201</v>
+        <v>0.0209</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0208</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>863</v>
+        <v>897</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01825</t>
+          <t>CM-26-01893</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Cuvée Etoile Rosé</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ott</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2762</v>
+        <v>494</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>16'897.97</t>
+          <t>7'134.74</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0202</v>
+        <v>0.0261</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0209</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0205</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>897</v>
+        <v>922</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01893</t>
+          <t>CM-26-01875</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Ygrec de Ch. d'Yquem</t>
+          <t>Le Difese</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -4690,182 +4682,182 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château d'Yquem</t>
+          <t>Tenuta San Guido</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>494</v>
+        <v>748</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>7'134.74</t>
+          <t>1'563.78</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0261</v>
+        <v>0.0289</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0019</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0192</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>922</v>
+        <v>936</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01875</t>
+          <t>CM-26-01841</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Le Difese</t>
+          <t>Champagne Brut Cuvée Argonne</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Tenuta San Guido</t>
+          <t>Henri Giraud</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>748</v>
+        <v>3042</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>1'563.78</t>
+          <t>25'571.66</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0019</v>
+        <v>0.0317</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0181</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>936</v>
+        <v>979</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01841</t>
+          <t>CM-26-01913</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Champagne Brut Cuvée Argonne</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Henri Giraud</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3042</v>
+        <v>763</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>25'571.66</t>
+          <t>11'063.16</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0317</v>
+        <v>0.0137</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0177</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>979</v>
+        <v>1005</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01913</t>
+          <t>CM-26-01900</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Meursault Perrières</t>
+          <t>Bourgogne Chardonnay</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -4879,38 +4871,38 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>763</v>
+        <v>800</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>11'063.16</t>
+          <t>2'668.29</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.017</v>
+        <v>0.0215</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0137</v>
+        <v>0.0033</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0157</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>1005</v>
+        <v>1058</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01900</t>
+          <t>CM-26-01847</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -4920,149 +4912,149 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Bourgogne Chardonnay</t>
+          <t>Aalto</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ballot-Millot</t>
+          <t>Aalto Bodegas y Viñedos</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>800</v>
+        <v>1664</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2'668.29</t>
+          <t>7'074.83</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0215</v>
+        <v>0.0129</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0033</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0142</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01847</t>
+          <t>CM-26-01837</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Aalto</t>
+          <t>Ausone</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Aalto Bodegas y Viñedos</t>
+          <t>Château Ausone</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1664</v>
+        <v>1926</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>7'074.83</t>
+          <t>12'907.55</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0129</v>
+        <v>0.0067</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0113</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01837</t>
+          <t>CM-26-01801</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Ausone</t>
+          <t>Champagne Dom Pérignon (Limited Edition Legacy)</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Ausone</t>
+          <t>Dom Pérignon</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1926</v>
+        <v>2540</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -5071,106 +5063,106 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>12'907.55</t>
+          <t>12'675.17</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
         <v>0.0067</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.016</v>
+        <v>0.0157</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0104</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>1069</v>
+        <v>1098</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01801</t>
+          <t>CM-26-01909</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Champagne Dom Pérignon (Limited Edition Legacy)</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Dom Pérignon</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2540</v>
+        <v>1119</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>12'675.17</t>
+          <t>10'753.00</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0067</v>
+        <v>0.0058</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0157</v>
+        <v>0.0133</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0103</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01909</t>
+          <t>CM-26-01894</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -5179,89 +5171,89 @@
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1119</v>
+        <v>160</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>10'753.00</t>
+          <t>963.07</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0058</v>
+        <v>0.0136</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0133</v>
+        <v>0.0012</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>1101</v>
+        <v>1125</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01894</t>
+          <t>CM-26-01788</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Ygrec de Ch. d'Yquem</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Château d'Yquem</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>160</v>
+        <v>532</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>963.07</t>
+          <t>3'842.02</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0136</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0048</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0086</v>
+        <v>0.0068</v>
       </c>
     </row>
   </sheetData>
@@ -5302,14 +5294,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 01 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 02 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -5687,21 +5679,21 @@
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01695</t>
+          <t>CM-26-01711</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Grand Puy Lacoste</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -5711,167 +5703,167 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Grand Puy Lacoste</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>495</v>
+        <v>11</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>8.89%</t>
+          <t>9.09%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>23'490.85</t>
+          <t>459.98</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1915</v>
+        <v>0.1958</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0291</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1265</v>
+        <v>0.1177</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01711</t>
+          <t>CM-26-01761</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>459.98</t>
+          <t>48'468.66</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1958</v>
+        <v>0.1346</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1177</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01761</t>
+          <t>CM-26-01842</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>32</v>
+        <v>1076</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>48'468.66</t>
+          <t>154'116.50</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.1346</v>
+        <v>0.0321</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.06</v>
+        <v>0.1908</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1048</v>
+        <v>0.0956</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01842</t>
+          <t>CM-26-01786</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -5881,57 +5873,57 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1076</v>
+        <v>418</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>154'116.50</t>
+          <t>53'350.72</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0321</v>
+        <v>0.098</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1908</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0956</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01786</t>
+          <t>CM-26-01868</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -5941,67 +5933,67 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Haut Brion Blanc</t>
+          <t>Lodovico</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Tenuta di Biserno</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>418</v>
+        <v>163</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>53'350.72</t>
+          <t>21'470.52</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.098</v>
+        <v>0.1189</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0266</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0852</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01698</t>
+          <t>CM-26-01749</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Chapelle de la Mission Haut-Brion (2nd Vin)</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -6011,167 +6003,167 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château La Mission Haut Brion</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3950</v>
+        <v>3866</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>136'772.14</t>
+          <t>77'935.68</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.025</v>
+        <v>0.0485</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1693</v>
+        <v>0.0965</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0827</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>139</v>
+        <v>224</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01868</t>
+          <t>CM-26-01708</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Lodovico</t>
+          <t>Brane Cantenac</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Tenuta di Biserno</t>
+          <t>Château Brane Cantenac</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>163</v>
+        <v>1480</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>21'470.52</t>
+          <t>26'612.38</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.1189</v>
+        <v>0.0844</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.033</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.082</v>
+        <v>0.0638</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>140</v>
+        <v>244</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01701</t>
+          <t>CM-26-01750</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Reserve de la Comtesse (2nd Vin)</t>
+          <t>Latour</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Pichon-Longueville Comtesse de Lalande</t>
+          <t>Château Latour</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3667</v>
+        <v>1862</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>121'721.15</t>
+          <t>111'613.62</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1507</v>
+        <v>0.1382</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0609</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01738</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -6181,7 +6173,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Les Carmes Haut Brion</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -6191,57 +6183,57 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Les Carmes Haut-Brion</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3866</v>
+        <v>5146</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>77'935.68</t>
+          <t>97'063.91</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0485</v>
+        <v>0.0196</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0965</v>
+        <v>0.1202</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0677</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01708</t>
+          <t>CM-26-01705</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Brane Cantenac</t>
+          <t>Haut Bailly</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -6251,7 +6243,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Brane Cantenac</t>
+          <t>Château Haut Bailly</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -6260,48 +6252,48 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1480</v>
+        <v>4119</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>26'612.38</t>
+          <t>68'593.06</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0844</v>
+        <v>0.0418</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.033</v>
+        <v>0.0849</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0638</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>240</v>
+        <v>394</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01697</t>
+          <t>CM-26-01720</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Pavie</t>
+          <t>Trottevieille</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -6311,117 +6303,117 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Pavie</t>
+          <t>Château Trottevieille</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2842</v>
+        <v>707</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>89'026.43</t>
+          <t>10'823.31</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0295</v>
+        <v>0.067</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.1102</v>
+        <v>0.0134</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0618</v>
+        <v>0.0456</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>244</v>
+        <v>405</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01778</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Champagne Brut Grande Cuvée</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Krug</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1862</v>
+        <v>703</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>111'613.62</t>
+          <t>35'222.13</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0459</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1382</v>
+        <v>0.0436</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0609</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>253</v>
+        <v>418</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01714</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -6431,287 +6423,287 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>5146</v>
+        <v>401</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>97'063.91</t>
+          <t>25'015.66</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.0536</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.1202</v>
+        <v>0.031</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0598</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>265</v>
+        <v>437</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01705</t>
+          <t>CM-26-01843</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Grands Echézeaux</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Mongeard Mugneret</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4119</v>
+        <v>2297</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>68'593.06</t>
+          <t>58'066.22</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0418</v>
+        <v>0.0243</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0849</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.059</v>
+        <v>0.0433</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>394</v>
+        <v>489</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01720</t>
+          <t>CM-26-01945</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Trottevieille</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Château Trottevieille</t>
+          <t>Château Lafite Rothschild</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>707</v>
+        <v>1175</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>10'823.31</t>
+          <t>72'662.43</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.067</v>
+        <v>0.0073</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.0134</v>
+        <v>0.09</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0456</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>405</v>
+        <v>563</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01778</t>
+          <t>CM-26-01704</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Grande Cuvée</t>
+          <t>Sloan Red</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Krug</t>
+          <t>Sloan</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>703</v>
+        <v>332</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>35'222.13</t>
+          <t>24'356.51</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0459</v>
+        <v>0.039</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0436</v>
+        <v>0.0302</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0355</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>418</v>
+        <v>583</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01714</t>
+          <t>CM-26-01789</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>401</v>
+        <v>509</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>25'015.66</t>
+          <t>38'932.73</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0536</v>
+        <v>0.0254</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.031</v>
+        <v>0.0482</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0446</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>437</v>
+        <v>610</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01843</t>
+          <t>CM-26-01715</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -6721,67 +6713,67 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Grands Echézeaux</t>
+          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Mongeard Mugneret</t>
+          <t>Château Mouton Rothschild</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2297</v>
+        <v>439</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>58'066.22</t>
+          <t>18'907.18</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0243</v>
+        <v>0.0392</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0234</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0433</v>
+        <v>0.0329</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>489</v>
+        <v>692</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01945</t>
+          <t>CM-26-01716</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Léoville Poyferré</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -6791,98 +6783,98 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Château Léoville Poyferré</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1175</v>
+        <v>605</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>72'662.43</t>
+          <t>23'090.54</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0073</v>
+        <v>0.0284</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.09</v>
+        <v>0.0286</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0404</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>563</v>
+        <v>693</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01704</t>
+          <t>CM-26-01907</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Sloan Red</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>332</v>
+        <v>940</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>24'356.51</t>
+          <t>23'816.30</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.039</v>
+        <v>0.0276</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0302</v>
+        <v>0.0295</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0355</v>
+        <v>0.0284</v>
       </c>
     </row>
   </sheetData>
@@ -6930,7 +6922,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10043,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-22 11:35  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report.xlsx
+++ b/AVUwinnersCM/winners_report.xlsx
@@ -16,7 +16,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TOP 25 All-Time'!$A$3:$N$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last 7 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last 14 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last 21 Days'!$A$3:$N$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Last Month (May 2026)'!$A$3:$N$53</definedName>
@@ -29,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +57,10 @@
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00999999"/>
     </font>
   </fonts>
   <fills count="5">
@@ -109,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,6 +135,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -526,7 +530,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2132,14 +2136,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 16 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 23 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -2215,1428 +2219,14 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01868</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>🟨</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Lodovico</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Tenuta di Biserno</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>163</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>5.52%</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>21'470.52</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0.1189</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0.0266</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0.082</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="6" t="n">
-        <v>489</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01945</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Lafite Rothschild</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Château Lafite Rothschild</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>1175</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>0.34%</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>72'662.43</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0.0404</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>693</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01907</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Meursault Perrières</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Ballot-Millot</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>940</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>1.28%</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>23'816.30</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.0276</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0.0295</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0.0284</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>750</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01912</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Léoville Las Cases</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Château Léoville Las Cases</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>2662</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>36'543.63</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>0.0452</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0.0258</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>826</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01935</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>DRC Corton Charlemagne</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>0.72%</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>26'352.00</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0.0326</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0.0223</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="n">
-        <v>897</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01893</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Ygrec de Ch. d'Yquem</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Château d'Yquem</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>494</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>1.21%</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>7'134.74</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0.0261</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>0.0192</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>922</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01875</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Le Difese</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Tenuta San Guido</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>748</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>1.34%</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>1'563.78</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0.0289</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0.0181</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>979</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01913</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Meursault Perrières</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Ballot-Millot</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>763</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>0.79%</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>11'063.16</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0.0137</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>0.0157</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>1005</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01900</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Bourgogne Chardonnay</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Ballot-Millot</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>800</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>2'668.29</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0.0215</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0.0142</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>1098</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01909</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Champagne le Mesnil</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Maison Salon</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>1119</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>10'753.00</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0.0133</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>1101</v>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01894</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Ygrec de Ch. d'Yquem</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Château d'Yquem</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>963.07</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>0.0136</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="N14" s="4" t="n">
-        <v>0.0086</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>1126</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01895</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>💎</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Ygrec de Ch. d'Yquem</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Château d'Yquem</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>3616</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>7'002.23</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0.008699999999999999</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0.0067</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>1141</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01940</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>🩷</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Almaviva</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Baron Philippe de Rothschild and Concha Y Toro</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>3416</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>4'668.32</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0.0058</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0.0049</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>1273</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01925</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>DRC Corton Charlemagne</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>134</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>1274</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01922</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>🟣</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>DRC Romanée St. Vivant</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Domaine de la Romanée Conti</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="n">
-        <v>1275</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01896</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>1276</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01890</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>1277</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01889</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>1278</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01888</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="n">
-        <v>1279</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01884</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>257</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>1280</v>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01882</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="6" t="n">
-        <v>1281</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01881</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>1282</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01880</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="n">
-        <v>1283</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>CM-26-01879</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>55</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>1284</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>CM-26-01877</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>⚪</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>0</v>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>No data for this period.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N28"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
@@ -3673,14 +2263,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 09 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 16 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -3758,11 +2348,11 @@
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01782</t>
+          <t>CM-26-01868</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3772,367 +2362,367 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion Blanc</t>
+          <t>Lodovico</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Tenuta di Biserno</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>30.43%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>22'912.96</t>
+          <t>21'470.52</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.6554</v>
+        <v>0.1189</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.0284</v>
+        <v>0.0266</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.4046</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>40</v>
+        <v>489</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01836</t>
+          <t>CM-26-01945</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>La Dame de Montrose (2nd Vin)</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Château Montrose</t>
+          <t>Château Lafite Rothschild</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>3643</v>
+        <v>1175</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>196'646.81</t>
+          <t>72'662.43</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.2435</v>
+        <v>0.09</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1496</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>58</v>
+        <v>693</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01785</t>
+          <t>CM-26-01907</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion Blanc</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>461</v>
+        <v>940</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>127'563.05</t>
+          <t>23'816.30</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1122</v>
+        <v>0.0276</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1579</v>
+        <v>0.0295</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1305</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>105</v>
+        <v>750</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01842</t>
+          <t>CM-26-01912</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Léoville Las Cases</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1076</v>
+        <v>2662</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>16</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>154'116.50</t>
+          <t>36'543.63</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0321</v>
+        <v>0.0129</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1908</v>
+        <v>0.0452</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.0956</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>129</v>
+        <v>826</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01786</t>
+          <t>CM-26-01935</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion Blanc</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>418</v>
+        <v>138</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>53'350.72</t>
+          <t>26'352.00</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.098</v>
+        <v>0.0155</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0326</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.0852</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>139</v>
+        <v>897</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01868</t>
+          <t>CM-26-01893</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Lodovico</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Tenuta di Biserno</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>163</v>
+        <v>494</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>21'470.52</t>
+          <t>7'134.74</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1189</v>
+        <v>0.0261</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.082</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>437</v>
+        <v>922</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01843</t>
+          <t>CM-26-01875</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Grands Echézeaux</t>
+          <t>Le Difese</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -4142,67 +2732,67 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Mongeard Mugneret</t>
+          <t>Tenuta San Guido</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2297</v>
+        <v>748</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>58'066.22</t>
+          <t>1'563.78</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0243</v>
+        <v>0.0289</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0019</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0433</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>489</v>
+        <v>979</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01945</t>
+          <t>CM-26-01913</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -4211,158 +2801,158 @@
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1175</v>
+        <v>763</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>72'662.43</t>
+          <t>11'063.16</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0073</v>
+        <v>0.017</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.09</v>
+        <v>0.0137</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0404</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>583</v>
+        <v>1005</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01789</t>
+          <t>CM-26-01900</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>Bourgogne Chardonnay</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>509</v>
+        <v>800</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>38'932.73</t>
+          <t>2'668.29</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0254</v>
+        <v>0.0215</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.0033</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0345</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>693</v>
+        <v>1098</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01907</t>
+          <t>CM-26-01909</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Meursault Perrières</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ballot-Millot</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>940</v>
+        <v>1119</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>23'816.30</t>
+          <t>10'753.00</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.0276</v>
+        <v>0.0058</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0295</v>
+        <v>0.0133</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.0284</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>750</v>
+        <v>1101</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01912</t>
+          <t>CM-26-01894</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4372,117 +2962,117 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Léoville Las Cases</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Léoville Las Cases</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2662</v>
+        <v>160</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>36'543.63</t>
+          <t>963.07</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0129</v>
+        <v>0.0136</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0452</v>
+        <v>0.0012</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0258</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>826</v>
+        <v>1126</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01935</t>
+          <t>CM-26-01895</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>DRC Corton Charlemagne</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Domaine de la Romanée Conti</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>138</v>
+        <v>3616</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>26'352.00</t>
+          <t>7'002.23</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0155</v>
+        <v>0.0054</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.0326</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0223</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>853</v>
+        <v>1141</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01787</t>
+          <t>CM-26-01940</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4492,137 +3082,137 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>San Leonardo</t>
+          <t>Almaviva</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Tenuta San Leonardo</t>
+          <t>Baron Philippe de Rothschild and Concha Y Toro</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2115</v>
+        <v>3416</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>16'195.97</t>
+          <t>4'668.32</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.0043</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.0201</v>
+        <v>0.0058</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0208</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>863</v>
+        <v>1273</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01825</t>
+          <t>CM-26-01925</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Cuvée Etoile Rosé</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Domaine Ott</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2762</v>
+        <v>134</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>16'897.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0202</v>
+        <v>0</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.0209</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>897</v>
+        <v>1274</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01893</t>
+          <t>CM-26-01922</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Ygrec de Ch. d'Yquem</t>
+          <t>DRC Romanée St. Vivant</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château d'Yquem</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -4631,629 +3221,549 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>494</v>
+        <v>118</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>7'134.74</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0261</v>
+        <v>0</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.0192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>922</v>
+        <v>1275</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01875</t>
+          <t>CM-26-01896</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Le Difese</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Tenuta San Guido</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>748</v>
+        <v>11</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>1'563.78</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.0289</v>
+        <v>0</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0019</v>
+        <v>0</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>936</v>
+        <v>1276</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01841</t>
+          <t>CM-26-01890</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Cuvée Argonne</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Henri Giraud</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3042</v>
+        <v>13</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>25'571.66</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.008399999999999999</v>
+        <v>0</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0317</v>
+        <v>0</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>979</v>
+        <v>1277</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01913</t>
+          <t>CM-26-01889</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Meursault Perrières</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Domaine Ballot-Millot</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>763</v>
+        <v>13</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>11'063.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.0137</v>
+        <v>0</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0157</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>1005</v>
+        <v>1278</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01900</t>
+          <t>CM-26-01888</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Bourgogne Chardonnay</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Domaine Ballot-Millot</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>800</v>
+        <v>12</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>2'668.29</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0215</v>
+        <v>0</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0033</v>
+        <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>1058</v>
+        <v>1279</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01847</t>
+          <t>CM-26-01884</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Aalto</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>Aalto Bodegas y Viñedos</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1664</v>
+        <v>257</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>7'074.83</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0129</v>
+        <v>0</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.008800000000000001</v>
+        <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>1066</v>
+        <v>1280</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01837</t>
+          <t>CM-26-01882</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Ausone</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Château Ausone</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1926</v>
+        <v>33</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>12'907.55</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.0067</v>
+        <v>0</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>1069</v>
+        <v>1281</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01801</t>
+          <t>CM-26-01881</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Champagne Dom Pérignon (Limited Edition Legacy)</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Dom Pérignon</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2540</v>
+        <v>10</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>12'675.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0067</v>
+        <v>0</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0157</v>
+        <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>1098</v>
+        <v>1282</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01909</t>
+          <t>CM-26-01880</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Maison Salon</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1119</v>
+        <v>79</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>10'753.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0133</v>
+        <v>0</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>1101</v>
+        <v>1283</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01894</t>
+          <t>CM-26-01879</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Ygrec de Ch. d'Yquem</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Château d'Yquem</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>963.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0136</v>
+        <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>1125</v>
+        <v>1284</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01788</t>
+          <t>CM-26-01877</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>⚪</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion Blanc</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Château Haut Brion</t>
-        </is>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>532</v>
+        <v>191</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>3'842.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.008200000000000001</v>
+        <v>0</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0068</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5294,14 +3804,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 02 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 09 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -5439,21 +3949,21 @@
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="6" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01713</t>
+          <t>CM-26-01836</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>La Dame de Montrose (2nd Vin)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -5463,47 +3973,47 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Montrose</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>80</v>
+        <v>3643</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>27.50%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>99'331.85</t>
+          <t>196'646.81</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>0.5923</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.123</v>
+        <v>0.2435</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4046</v>
+        <v>0.1496</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01706</t>
+          <t>CM-26-01785</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -5513,7 +4023,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -5523,107 +4033,107 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3482</v>
+        <v>461</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>461'514.36</t>
+          <t>127'563.05</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0545</v>
+        <v>0.1122</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.5714</v>
+        <v>0.1579</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2613</v>
+        <v>0.1305</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01836</t>
+          <t>CM-26-01842</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>La Dame de Montrose (2nd Vin)</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Château Montrose</t>
+          <t>Château Margaux</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3643</v>
+        <v>1076</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>196'646.81</t>
+          <t>154'116.50</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0321</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2435</v>
+        <v>0.1908</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1496</v>
+        <v>0.0956</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01785</t>
+          <t>CM-26-01786</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5652,238 +4162,238 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>461</v>
+        <v>418</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>4.55%</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>127'563.05</t>
+          <t>53'350.72</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1122</v>
+        <v>0.098</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1579</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1305</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="n">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01711</t>
+          <t>CM-26-01868</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Lodovico</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Tenuta di Biserno</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>11</v>
+        <v>163</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>9.09%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>459.98</t>
+          <t>21'470.52</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>0.1958</v>
+        <v>0.1189</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0266</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.1177</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>91</v>
+        <v>437</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01761</t>
+          <t>CM-26-01843</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>Grands Echézeaux</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Mongeard Mugneret</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>32</v>
+        <v>2297</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>48'468.66</t>
+          <t>58'066.22</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1346</v>
+        <v>0.0243</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.06</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1048</v>
+        <v>0.0433</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="n">
-        <v>105</v>
+        <v>489</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01842</t>
+          <t>CM-26-01945</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Lafite Rothschild</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Château Margaux</t>
+          <t>Château Lafite Rothschild</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1076</v>
+        <v>1175</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>154'116.50</t>
+          <t>72'662.43</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>0.0321</v>
+        <v>0.0073</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>0.1908</v>
+        <v>0.09</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.0956</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>129</v>
+        <v>583</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01786</t>
+          <t>CM-26-01789</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Haut Brion Blanc</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Brion</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -5892,398 +4402,398 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>418</v>
+        <v>509</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>53'350.72</t>
+          <t>38'932.73</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.098</v>
+        <v>0.0254</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0482</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0852</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="n">
-        <v>139</v>
+        <v>693</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01868</t>
+          <t>CM-26-01907</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Lodovico</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Tenuta di Biserno</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>163</v>
+        <v>940</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>5.52%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>21'470.52</t>
+          <t>23'816.30</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>0.1189</v>
+        <v>0.0276</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.0266</v>
+        <v>0.0295</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.082</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>198</v>
+        <v>750</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01749</t>
+          <t>CM-26-01912</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Léoville Las Cases</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château Léoville Las Cases</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3866</v>
+        <v>2662</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>77'935.68</t>
+          <t>36'543.63</t>
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0485</v>
+        <v>0.0129</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0965</v>
+        <v>0.0452</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0677</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="n">
-        <v>224</v>
+        <v>826</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01708</t>
+          <t>CM-26-01935</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Brane Cantenac</t>
+          <t>DRC Corton Charlemagne</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Château Brane Cantenac</t>
+          <t>Domaine de la Romanée Conti</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1480</v>
+        <v>138</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>26'612.38</t>
+          <t>26'352.00</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.0844</v>
+        <v>0.0155</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.033</v>
+        <v>0.0326</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0.0638</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>244</v>
+        <v>853</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01750</t>
+          <t>CM-26-01787</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🩷</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Latour</t>
+          <t>San Leonardo</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Château Latour</t>
+          <t>Tenuta San Leonardo</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1862</v>
+        <v>2115</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>111'613.62</t>
+          <t>16'195.97</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0213</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1382</v>
+        <v>0.0201</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0609</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>253</v>
+        <v>863</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01738</t>
+          <t>CM-26-01825</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Les Carmes Haut Brion</t>
+          <t>Cuvée Etoile Rosé</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Château Les Carmes Haut-Brion</t>
+          <t>Domaine Ott</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>5146</v>
+        <v>2762</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>97'063.91</t>
+          <t>16'897.97</t>
         </is>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.0196</v>
+        <v>0.0202</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.1202</v>
+        <v>0.0209</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.0598</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>265</v>
+        <v>897</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01705</t>
+          <t>CM-26-01893</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>🩷</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Haut Bailly</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Château Haut Bailly</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4119</v>
+        <v>494</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>68'593.06</t>
+          <t>7'134.74</t>
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.0418</v>
+        <v>0.0261</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0849</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.059</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>394</v>
+        <v>922</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01720</t>
+          <t>CM-26-01875</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -6293,297 +4803,297 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Trottevieille</t>
+          <t>Le Difese</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>Château Trottevieille</t>
+          <t>Tenuta San Guido</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>707</v>
+        <v>748</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>10'823.31</t>
+          <t>1'563.78</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.067</v>
+        <v>0.0289</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.0134</v>
+        <v>0.0019</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.0456</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>405</v>
+        <v>936</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01778</t>
+          <t>CM-26-01841</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Champagne Brut Grande Cuvée</t>
+          <t>Champagne Brut Cuvée Argonne</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Krug</t>
+          <t>Henri Giraud</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>703</v>
+        <v>3042</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>35'222.13</t>
+          <t>25'571.66</t>
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0459</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0436</v>
+        <v>0.0317</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.045</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>418</v>
+        <v>979</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01714</t>
+          <t>CM-26-01913</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Meursault Perrières</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>401</v>
+        <v>763</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>25'015.66</t>
+          <t>11'063.16</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>0.0536</v>
+        <v>0.017</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0.031</v>
+        <v>0.0137</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.0446</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>437</v>
+        <v>1005</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01843</t>
+          <t>CM-26-01900</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Grands Echézeaux</t>
+          <t>Bourgogne Chardonnay</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Mongeard Mugneret</t>
+          <t>Domaine Ballot-Millot</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2297</v>
+        <v>800</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>58'066.22</t>
+          <t>2'668.29</t>
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0243</v>
+        <v>0.0215</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0033</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0433</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="n">
-        <v>489</v>
+        <v>1058</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01945</t>
+          <t>CM-26-01847</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Lafite Rothschild</t>
+          <t>Aalto</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>Château Lafite Rothschild</t>
+          <t>Aalto Bodegas y Viñedos</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1175</v>
+        <v>1664</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>72'662.43</t>
+          <t>7'074.83</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0073</v>
+        <v>0.0129</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.09</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.0404</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>563</v>
+        <v>1066</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01704</t>
+          <t>CM-26-01837</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -6593,177 +5103,177 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Sloan Red</t>
+          <t>Ausone</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Sloan</t>
+          <t>Château Ausone</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>332</v>
+        <v>1926</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>6</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>24'356.51</t>
+          <t>12'907.55</t>
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.039</v>
+        <v>0.0067</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.0302</v>
+        <v>0.016</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.0355</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="n">
-        <v>583</v>
+        <v>1069</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01789</t>
+          <t>CM-26-01801</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>🟣</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Champagne le Mesnil</t>
+          <t>Champagne Dom Pérignon (Limited Edition Legacy)</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>Maison Salon</t>
+          <t>Dom Pérignon</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>509</v>
+        <v>2540</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>38'932.73</t>
+          <t>12'675.17</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0254</v>
+        <v>0.0067</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.0482</v>
+        <v>0.0157</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.0345</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>610</v>
+        <v>1098</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01715</t>
+          <t>CM-26-01909</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>🟨</t>
+          <t>🟣</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Le Petit Mouton Rothschild (2nd Vin)</t>
+          <t>Champagne le Mesnil</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Château Mouton Rothschild</t>
+          <t>Maison Salon</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>439</v>
+        <v>1119</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>18'907.18</t>
+          <t>10'753.00</t>
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0392</v>
+        <v>0.0058</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0234</v>
+        <v>0.0133</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0329</v>
+        <v>0.008800000000000001</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="n">
-        <v>692</v>
+        <v>1101</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CM-26-01716</t>
+          <t>CM-26-01894</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -6773,108 +5283,108 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Léoville Poyferré</t>
+          <t>Ygrec de Ch. d'Yquem</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Château Léoville Poyferré</t>
+          <t>Château d'Yquem</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>605</v>
+        <v>160</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>23'090.54</t>
+          <t>963.07</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>0.0284</v>
+        <v>0.0136</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0.0286</v>
+        <v>0.0012</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.0285</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>693</v>
+        <v>1125</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CM-26-01907</t>
+          <t>CM-26-01788</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>🟨</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Meursault Perrières</t>
+          <t>Haut Brion Blanc</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Domaine Ballot-Millot</t>
+          <t>Château Haut Brion</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>940</v>
+        <v>532</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>23'816.30</t>
+          <t>3'842.02</t>
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0276</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0295</v>
+        <v>0.0048</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0284</v>
+        <v>0.0068</v>
       </c>
     </row>
   </sheetData>
@@ -6922,7 +5432,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>
@@ -10043,7 +8553,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-23 14:36  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
+          <t>Generated: 2026-06-30 14:30  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 10 (all campaigns incl. small sends)</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report.xlsx
+++ b/AVUwinnersCM/winners_report.xlsx
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 16:48  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45</t>
+          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 16:48  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 7</t>
+          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 7</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 16:48  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 21</t>
+          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 21</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 16:48  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 42</t>
+          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 41</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 16:48  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 120</t>
+          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 120</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 16:48  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45</t>
+          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45</t>
         </is>
       </c>
     </row>

--- a/AVUwinnersCM/winners_report.xlsx
+++ b/AVUwinnersCM/winners_report.xlsx
@@ -526,7 +526,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45</t>
+          <t>Generated: 2026-07-21 12:00  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45</t>
         </is>
       </c>
     </row>
@@ -2132,14 +2132,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 13 Jul 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 7 Days (since 14 Jul 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 7</t>
+          <t>Generated: 2026-07-21 12:00  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 7</t>
         </is>
       </c>
     </row>
@@ -2673,14 +2673,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 06 Jul 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 14 Days (since 07 Jul 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 21</t>
+          <t>Generated: 2026-07-21 12:00  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 21</t>
         </is>
       </c>
     </row>
@@ -4054,14 +4054,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 29 Jun 2026)</t>
+          <t>📅 CAMPAIGN WINNERS — Last 21 Days (since 30 Jun 2026)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 41</t>
+          <t>Generated: 2026-07-21 12:00  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 41</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 120</t>
+          <t>Generated: 2026-07-21 12:00  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45  |  Qualifying rows this period: 120</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-20 17:39  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45</t>
+          <t>Generated: 2026-07-21 12:00  |  Scoring: 60% Conv + 40% Sales  |  Excl: HORECA/TRADE/Leads/Delayed  |  email &gt;= 100  |  bottle price &gt;= CHF 45</t>
         </is>
       </c>
     </row>
